--- a/example1-metabolomics/results-A/pca/pca_norm_MaleMRD_MaleMHFD_FemMRD_FemMHFD.xlsx
+++ b/example1-metabolomics/results-A/pca/pca_norm_MaleMRD_MaleMHFD_FemMRD_FemMHFD.xlsx
@@ -560,73 +560,73 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.251654854427229</v>
+        <v>-0.250133794220341</v>
       </c>
       <c r="C2" t="n">
-        <v>0.252761786527895</v>
+        <v>-0.261364355147002</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0784332793666552</v>
+        <v>0.0739582217376572</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00213513927764798</v>
+        <v>-0.0166424772388387</v>
       </c>
       <c r="F2" t="n">
-        <v>0.233791731995436</v>
+        <v>-0.225026481698752</v>
       </c>
       <c r="G2" t="n">
-        <v>0.124643028715074</v>
+        <v>0.0913074226421297</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.195110669249412</v>
+        <v>-0.188778459554685</v>
       </c>
       <c r="I2" t="n">
-        <v>0.305634319758928</v>
+        <v>0.319321045462256</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0233165565216358</v>
+        <v>-0.0570307224606482</v>
       </c>
       <c r="K2" t="n">
-        <v>0.286303766604613</v>
+        <v>0.173694237421022</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.459759443336806</v>
+        <v>-0.540680406892767</v>
       </c>
       <c r="M2" t="n">
-        <v>0.373850939907303</v>
+        <v>0.242758020391149</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0213479977326666</v>
+        <v>-0.0848485446206457</v>
       </c>
       <c r="O2" t="n">
-        <v>0.29285761676048</v>
+        <v>0.369121327794835</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.111757388656852</v>
+        <v>-0.0917327039762728</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0793714688647742</v>
+        <v>0.0315997590160704</v>
       </c>
       <c r="R2" t="n">
-        <v>0.067494592401229</v>
+        <v>-0.102320215301899</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0285065942537464</v>
+        <v>0.0204909722426489</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.314478041198057</v>
+        <v>-0.313650333661407</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0153569292642877</v>
+        <v>0.0175751433680067</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0636614210817283</v>
+        <v>0.0394883587067063</v>
       </c>
       <c r="W2" t="n">
-        <v>0.133149997204031</v>
+        <v>-0.13452087394138</v>
       </c>
       <c r="X2" t="n">
-        <v>0.000493960811921814</v>
+        <v>0.00395403793952962</v>
       </c>
     </row>
     <row r="3">
@@ -634,73 +634,73 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.200905186844314</v>
+        <v>-0.201634110545817</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0984555496327298</v>
+        <v>-0.0929748986985314</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.141668937721742</v>
+        <v>0.120448973663513</v>
       </c>
       <c r="E3" t="n">
-        <v>0.214479509342595</v>
+        <v>-0.186181815993656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.202834603832974</v>
+        <v>-0.225550200461541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0963524899518486</v>
+        <v>0.0929428414542565</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0116192487521632</v>
+        <v>0.0372807205035996</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0604915375843612</v>
+        <v>-0.0557090077175522</v>
       </c>
       <c r="J3" t="n">
-        <v>0.146900016083027</v>
+        <v>0.154736853891095</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.373944850580485</v>
+        <v>-0.347565603591539</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.332062389054083</v>
+        <v>-0.127352909093815</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.509814869802926</v>
+        <v>-0.619024295903041</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0031330790651203</v>
+        <v>-0.00399010220842863</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.130682663756913</v>
+        <v>-0.0934905864365593</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.130554432739444</v>
+        <v>-0.216623716232791</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.418717771737041</v>
+        <v>0.397209040880249</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0456595183259408</v>
+        <v>-0.0579975499026318</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.209815673629172</v>
+        <v>-0.17527396310163</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.11954912090984</v>
+        <v>-0.139608137951743</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.090281332589946</v>
+        <v>-0.019731917625688</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0463902092091406</v>
+        <v>0.0829985462412154</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.127495877785474</v>
+        <v>0.131536110938761</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0405829513886226</v>
+        <v>-0.0419010884119626</v>
       </c>
     </row>
     <row r="4">
@@ -708,73 +708,73 @@
         <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.265702291443741</v>
+        <v>-0.264373440842387</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.049741415189584</v>
+        <v>0.02739143892673</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.28346720656957</v>
+        <v>0.301746438062451</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0242212674702412</v>
+        <v>-0.0156487602843564</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0887740811210669</v>
+        <v>-0.0562030268692791</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.128037363358409</v>
+        <v>-0.151661514846319</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.230040965887837</v>
+        <v>-0.208233104547813</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.240393860440976</v>
+        <v>-0.179492837559351</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.460241966308452</v>
+        <v>-0.433302208752979</v>
       </c>
       <c r="K4" t="n">
-        <v>0.313951137253694</v>
+        <v>0.380158172086074</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0472570717536777</v>
+        <v>0.0837863519597499</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.252001113916649</v>
+        <v>-0.237613511051463</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.00110768383993813</v>
+        <v>0.016638807340357</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.207089666449808</v>
+        <v>-0.198643644218377</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.241056138141018</v>
+        <v>-0.232265956871486</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.324256237693994</v>
+        <v>-0.302850925589378</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0707754266743559</v>
+        <v>0.170541349710642</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.264656438150216</v>
+        <v>-0.273948294047583</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.030012955326541</v>
+        <v>-0.028684223137799</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.114708990930309</v>
+        <v>-0.0728123976637045</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0393081710513115</v>
+        <v>0.0819118465875613</v>
       </c>
       <c r="W4" t="n">
-        <v>0.181511544770712</v>
+        <v>-0.183995346787079</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0716889227622797</v>
+        <v>0.0659388351629229</v>
       </c>
     </row>
     <row r="5">
@@ -782,73 +782,73 @@
         <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.16818961095858</v>
+        <v>-0.166865245070916</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0807332838793937</v>
+        <v>-0.0932636591748192</v>
       </c>
       <c r="D5" t="n">
-        <v>0.046526723943149</v>
+        <v>-0.0318387136520327</v>
       </c>
       <c r="E5" t="n">
-        <v>0.254212221428291</v>
+        <v>-0.280592186505226</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.198399460713003</v>
+        <v>0.208613881666319</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.265021658852903</v>
+        <v>-0.216525901998767</v>
       </c>
       <c r="H5" t="n">
-        <v>0.253870761930093</v>
+        <v>0.248899466804898</v>
       </c>
       <c r="I5" t="n">
-        <v>0.067765635128304</v>
+        <v>-0.0310927183229831</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.482578111245963</v>
+        <v>-0.47070914690647</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.298362565542742</v>
+        <v>-0.34174174161152</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0900053200277276</v>
+        <v>-0.0549116720949142</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0412321292399024</v>
+        <v>0.0368859179490425</v>
       </c>
       <c r="N5" t="n">
-        <v>0.277234883639758</v>
+        <v>0.28848861024353</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.024493590558733</v>
+        <v>-0.015437052522269</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0463900298188424</v>
+        <v>0.0322350061158124</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0201472345881147</v>
+        <v>0.0165193589961049</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0285484568453676</v>
+        <v>-0.000138999593875272</v>
       </c>
       <c r="S5" t="n">
-        <v>0.190997319385123</v>
+        <v>0.218139273146386</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.219158972923603</v>
+        <v>-0.219435235330028</v>
       </c>
       <c r="U5" t="n">
-        <v>0.348598873366985</v>
+        <v>0.135824150554801</v>
       </c>
       <c r="V5" t="n">
-        <v>0.270660361139997</v>
+        <v>-0.402407870708261</v>
       </c>
       <c r="W5" t="n">
-        <v>0.166074595082766</v>
+        <v>-0.163015675082535</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0189696095314694</v>
+        <v>-0.01392642361097</v>
       </c>
     </row>
     <row r="6">
@@ -856,73 +856,73 @@
         <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0153867763159679</v>
+        <v>-0.0185392769547256</v>
       </c>
       <c r="C6" t="n">
-        <v>0.114203219179143</v>
+        <v>-0.0895006519252628</v>
       </c>
       <c r="D6" t="n">
-        <v>0.214443526599986</v>
+        <v>-0.240984219084617</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.135805628989074</v>
+        <v>0.154169254975938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.382307357900888</v>
+        <v>-0.352217413212905</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.769330256237944</v>
+        <v>-0.781762561045048</v>
       </c>
       <c r="H6" t="n">
-        <v>0.197404305951113</v>
+        <v>0.240369087856564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.17675709129524</v>
+        <v>0.142006886304384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0825478234726865</v>
+        <v>0.0299402189607515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0921968356173416</v>
+        <v>0.0351799490483556</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0130379812709819</v>
+        <v>-0.043770361804837</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0668851318978731</v>
+        <v>-0.0210364266328839</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.227710385235498</v>
+        <v>-0.198150086130735</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0596212970341578</v>
+        <v>-0.109693010920016</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0873369008301957</v>
+        <v>0.101479179412122</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0354946446296147</v>
+        <v>0.026794729902107</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0790169328198981</v>
+        <v>-0.0720937562975013</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.132627410900922</v>
+        <v>-0.134994326003901</v>
       </c>
       <c r="T6" t="n">
-        <v>0.042753242893719</v>
+        <v>0.0351079760329584</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0118501970468329</v>
+        <v>0.0508078323143868</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0564697124654559</v>
+        <v>0.0426813630021442</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0183119087009403</v>
+        <v>0.0190986470647924</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0217653205595097</v>
+        <v>0.0206266007737464</v>
       </c>
     </row>
     <row r="7">
@@ -930,73 +930,73 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.203409317544776</v>
+        <v>-0.203075770252479</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0726552599524552</v>
+        <v>-0.0710176698257305</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0770521828767479</v>
+        <v>0.0690250406820729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0400096072939198</v>
+        <v>-0.0337341820640613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.264800256037705</v>
+        <v>-0.270193597492195</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0941824140427946</v>
+        <v>0.0699190852102786</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0350049657976778</v>
+        <v>-0.0674379408902965</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.120109009505307</v>
+        <v>-0.109002378848716</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0369305190294837</v>
+        <v>0.0413823437853988</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.112206685724416</v>
+        <v>-0.0840947463521994</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00714991667651356</v>
+        <v>0.059489956940421</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0577712715777229</v>
+        <v>-0.0967603135274559</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.27544225441201</v>
+        <v>-0.273343625390155</v>
       </c>
       <c r="O7" t="n">
-        <v>0.166697114003956</v>
+        <v>0.170164948997614</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.318556854572434</v>
+        <v>-0.194261690819222</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.189716216948388</v>
+        <v>-0.34133173306815</v>
       </c>
       <c r="R7" t="n">
-        <v>0.264625005036591</v>
+        <v>-0.261087254432463</v>
       </c>
       <c r="S7" t="n">
-        <v>0.28617194367152</v>
+        <v>0.247918370535115</v>
       </c>
       <c r="T7" t="n">
-        <v>0.452107848777389</v>
+        <v>0.452075492731572</v>
       </c>
       <c r="U7" t="n">
-        <v>0.393131757444643</v>
+        <v>0.22999940444505</v>
       </c>
       <c r="V7" t="n">
-        <v>0.255896560091552</v>
+        <v>-0.409270628716687</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.127569597495265</v>
+        <v>0.137692254959547</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00807453632106615</v>
+        <v>0.0228936931091011</v>
       </c>
     </row>
     <row r="8">
@@ -1004,73 +1004,73 @@
         <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.265472471778779</v>
+        <v>-0.265098543026144</v>
       </c>
       <c r="C8" t="n">
-        <v>0.690185871274451</v>
+        <v>-0.678087457078412</v>
       </c>
       <c r="D8" t="n">
-        <v>0.150819720129787</v>
+        <v>-0.181697607495535</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.39289037640264</v>
+        <v>0.420388654823833</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.420862795358006</v>
+        <v>0.396277199211588</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0497219151348885</v>
+        <v>0.0789391775574733</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0974074993051503</v>
+        <v>0.0984951883232223</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.166560817339454</v>
+        <v>-0.170680294143537</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0622706383885408</v>
+        <v>0.058680453593818</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0284595415775917</v>
+        <v>0.0473723025203217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0578278111499379</v>
+        <v>0.0755049967570031</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.106121167828043</v>
+        <v>-0.0865358107230669</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.149568518804337</v>
+        <v>-0.136741886183853</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0793791669111827</v>
+        <v>-0.096050216222739</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0315024766132921</v>
+        <v>-0.0288590939327836</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.00320269273662781</v>
+        <v>-0.0125567661576345</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.0392632011485776</v>
+        <v>0.0249979303314106</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0477694710933052</v>
+        <v>0.0542969276438695</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0515853400341372</v>
+        <v>-0.0534393375245903</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.024768545060812</v>
+        <v>-0.0089886149928597</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0252681038832668</v>
+        <v>0.0374494453149544</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0473323420227684</v>
+        <v>0.0460322814719787</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0168889173993757</v>
+        <v>0.0160284871321886</v>
       </c>
     </row>
     <row r="9">
@@ -1078,73 +1078,73 @@
         <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.192386917066347</v>
+        <v>-0.191922722423841</v>
       </c>
       <c r="C9" t="n">
-        <v>0.151030640386282</v>
+        <v>-0.158565689287214</v>
       </c>
       <c r="D9" t="n">
-        <v>0.173316620082533</v>
+        <v>-0.162595221288392</v>
       </c>
       <c r="E9" t="n">
-        <v>0.368796051029586</v>
+        <v>-0.394752699321388</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.167610669454878</v>
+        <v>0.191235389393066</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.155429259084432</v>
+        <v>-0.132782468244946</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.111621545467408</v>
+        <v>-0.0291047469756026</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0987686796929875</v>
+        <v>0.108951464260276</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0751147184807562</v>
+        <v>-0.0459397899431504</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.240375959814486</v>
+        <v>-0.218854971393032</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0556930274780595</v>
+        <v>-0.0010026411818793</v>
       </c>
       <c r="M9" t="n">
-        <v>0.126090320020682</v>
+        <v>0.044956607773593</v>
       </c>
       <c r="N9" t="n">
-        <v>0.133644531256189</v>
+        <v>0.104385853443123</v>
       </c>
       <c r="O9" t="n">
-        <v>0.320564764356746</v>
+        <v>0.354121267978679</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0406555560455273</v>
+        <v>0.00312735691248591</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.272874821889306</v>
+        <v>-0.214110701512897</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.07074045452379</v>
+        <v>0.174973885527279</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.161666318094315</v>
+        <v>-0.194520587417399</v>
       </c>
       <c r="T9" t="n">
-        <v>0.373471125687912</v>
+        <v>0.390163146133502</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.408429624718648</v>
+        <v>-0.23003512680189</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.200498463054481</v>
+        <v>0.372815470289274</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.198332339663857</v>
+        <v>0.194345597419185</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0594234927472456</v>
+        <v>-0.0655390196381967</v>
       </c>
     </row>
     <row r="10">
@@ -1152,73 +1152,73 @@
         <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.15392155779363</v>
+        <v>-0.15614484605849</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0299891947933991</v>
+        <v>-0.0100157185957764</v>
       </c>
       <c r="D10" t="n">
-        <v>0.16626139331242</v>
+        <v>-0.191542080531799</v>
       </c>
       <c r="E10" t="n">
-        <v>0.225278620868889</v>
+        <v>-0.180520643535108</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.00856705201647836</v>
+        <v>-0.0257847409536108</v>
       </c>
       <c r="G10" t="n">
-        <v>0.114316359559874</v>
+        <v>0.13584815296402</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0926528765952007</v>
+        <v>0.136168115128639</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0496455353661523</v>
+        <v>-0.0313401984679359</v>
       </c>
       <c r="J10" t="n">
-        <v>0.131862195494555</v>
+        <v>0.126351639924925</v>
       </c>
       <c r="K10" t="n">
-        <v>0.235474896252654</v>
+        <v>0.255525301110818</v>
       </c>
       <c r="L10" t="n">
-        <v>0.14403635485874</v>
+        <v>0.0913582414164812</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0226042120546999</v>
+        <v>0.022094183142815</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0322360386673475</v>
+        <v>-0.0223573795783332</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0547154111098663</v>
+        <v>0.0312119148825671</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0723777577635026</v>
+        <v>0.0709218482945343</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0850402043014404</v>
+        <v>0.127576213864041</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.169377126045608</v>
+        <v>0.161882795595072</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.317585677415153</v>
+        <v>-0.27047555293419</v>
       </c>
       <c r="T10" t="n">
-        <v>0.158307560404638</v>
+        <v>0.110063550437599</v>
       </c>
       <c r="U10" t="n">
-        <v>0.339367583719062</v>
+        <v>0.408768761404308</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0879176724486669</v>
+        <v>-0.103521262624543</v>
       </c>
       <c r="W10" t="n">
-        <v>0.315236923121066</v>
+        <v>-0.289026351629132</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.620760086165387</v>
+        <v>-0.617984625949893</v>
       </c>
     </row>
     <row r="11">
@@ -1226,73 +1226,73 @@
         <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.243902432883797</v>
+        <v>-0.24241798566453</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.247346244335922</v>
+        <v>0.250917274843247</v>
       </c>
       <c r="D11" t="n">
-        <v>0.730184660417585</v>
+        <v>-0.676279056301783</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.261285144760354</v>
+        <v>0.178896578897017</v>
       </c>
       <c r="F11" t="n">
-        <v>0.210800201022996</v>
+        <v>-0.136207219821008</v>
       </c>
       <c r="G11" t="n">
-        <v>0.153640803618397</v>
+        <v>0.0694261152612344</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.272951954348605</v>
+        <v>-0.488179788464065</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.189532838490495</v>
+        <v>-0.187102287512972</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.150082802175986</v>
+        <v>-0.144459649741986</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.101522791332117</v>
+        <v>-0.113640520759895</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.137900065290056</v>
+        <v>-0.099677294170525</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0600469434985603</v>
+        <v>-0.0754629135626235</v>
       </c>
       <c r="N11" t="n">
-        <v>0.137168558401149</v>
+        <v>0.14191707907358</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0603040610284536</v>
+        <v>-0.0715700943354722</v>
       </c>
       <c r="P11" t="n">
-        <v>0.119393318666898</v>
+        <v>0.0982088761475354</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0013033911438044</v>
+        <v>0.0252115673278044</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0244579867006487</v>
+        <v>-0.01778605173951</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0708004884945329</v>
+        <v>0.0654009183110075</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0226698796980379</v>
+        <v>-0.0139703867091025</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0173919693949862</v>
+        <v>-0.0388450943247883</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00808553437412882</v>
+        <v>0.00349467649757665</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0272744687704101</v>
+        <v>-0.0306484227143215</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00505592969158372</v>
+        <v>0.00345530666228377</v>
       </c>
     </row>
     <row r="12">
@@ -1300,73 +1300,73 @@
         <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.192848383415186</v>
+        <v>-0.189283466830231</v>
       </c>
       <c r="C12" t="n">
-        <v>0.288710775571476</v>
+        <v>-0.30986318551486</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.110857187325212</v>
+        <v>0.124193992978512</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0886327193150183</v>
+        <v>-0.141239693924154</v>
       </c>
       <c r="F12" t="n">
-        <v>0.329693230244734</v>
+        <v>-0.298306189955992</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0697851135192314</v>
+        <v>0.0280711811782259</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.266816906355881</v>
+        <v>-0.273028348140219</v>
       </c>
       <c r="I12" t="n">
-        <v>0.182998864201492</v>
+        <v>0.225416883135404</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0830832161375137</v>
+        <v>0.131520328935247</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.206935619331104</v>
+        <v>-0.128973713186371</v>
       </c>
       <c r="L12" t="n">
-        <v>0.541942143786804</v>
+        <v>0.476176338399296</v>
       </c>
       <c r="M12" t="n">
-        <v>0.167566735379014</v>
+        <v>0.30981042707976</v>
       </c>
       <c r="N12" t="n">
-        <v>0.271534640684776</v>
+        <v>0.284029216080931</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.342919881127026</v>
+        <v>-0.355993946816962</v>
       </c>
       <c r="P12" t="n">
-        <v>0.134832816442085</v>
+        <v>0.0739332796298686</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0195800512089147</v>
+        <v>0.023034460697071</v>
       </c>
       <c r="R12" t="n">
-        <v>0.196940687074534</v>
+        <v>-0.179285689903236</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0739764562883604</v>
+        <v>0.0412261190888507</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0444285648036559</v>
+        <v>-0.0288109641333617</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0227247248261178</v>
+        <v>-0.00951022511085771</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0927459762775305</v>
+        <v>0.0891338742789128</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0628086460695196</v>
+        <v>-0.0677891890065637</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.0193503268488559</v>
+        <v>-0.0170011573577041</v>
       </c>
     </row>
     <row r="13">
@@ -1374,73 +1374,73 @@
         <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.198761194829506</v>
+        <v>-0.200231012093647</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0497864308091376</v>
+        <v>0.0567170606518112</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0378611849690282</v>
+        <v>-0.0493950637217355</v>
       </c>
       <c r="E13" t="n">
-        <v>0.309523983080153</v>
+        <v>-0.279595633130325</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0783833589169155</v>
+        <v>0.0539857722423381</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0438808280706215</v>
+        <v>-0.00598676049864697</v>
       </c>
       <c r="H13" t="n">
-        <v>0.155361518634422</v>
+        <v>0.209759983707749</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0107932686932792</v>
+        <v>-0.010378129644007</v>
       </c>
       <c r="J13" t="n">
-        <v>0.323917815104815</v>
+        <v>0.314708136246283</v>
       </c>
       <c r="K13" t="n">
-        <v>0.391455253084473</v>
+        <v>0.343055416867863</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.190276548357471</v>
+        <v>-0.297606755005922</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.268339256224109</v>
+        <v>-0.207501427710237</v>
       </c>
       <c r="N13" t="n">
-        <v>0.200352708002998</v>
+        <v>0.186156401800683</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.216228120229928</v>
+        <v>-0.306296918938803</v>
       </c>
       <c r="P13" t="n">
-        <v>0.157958701360958</v>
+        <v>0.199512187883631</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.214954447848643</v>
+        <v>-0.240118360242394</v>
       </c>
       <c r="R13" t="n">
-        <v>0.180375272159957</v>
+        <v>-0.153134692531568</v>
       </c>
       <c r="S13" t="n">
-        <v>0.482182247605757</v>
+        <v>0.414626531007911</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.004154733907567</v>
+        <v>0.0350014264890195</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.184704393864928</v>
+        <v>-0.202472648355445</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0211096298800443</v>
+        <v>0.107563630607017</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0540426643204823</v>
+        <v>-0.0610296548924851</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0386799497909055</v>
+        <v>-0.0430214204529474</v>
       </c>
     </row>
     <row r="14">
@@ -1448,73 +1448,73 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.249929476535373</v>
+        <v>-0.249458403190426</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.179229571652267</v>
+        <v>0.169797395698929</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0839291261586621</v>
+        <v>0.0994902829776912</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0227214579529996</v>
+        <v>0.020586506250491</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.261311162765228</v>
+        <v>0.257569105163938</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0748312593050564</v>
+        <v>0.0957122910937978</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0261683638570016</v>
+        <v>0.0276189258806833</v>
       </c>
       <c r="I14" t="n">
-        <v>0.164393701729761</v>
+        <v>0.128780637088538</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.054155616917148</v>
+        <v>-0.0799461982513966</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0822830205605321</v>
+        <v>-0.152742133965749</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.160379454372753</v>
+        <v>-0.177610909978849</v>
       </c>
       <c r="M14" t="n">
-        <v>0.186618013832687</v>
+        <v>0.173834720745376</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.318615039224661</v>
+        <v>-0.322597654323256</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.276911849544864</v>
+        <v>-0.281301680428051</v>
       </c>
       <c r="P14" t="n">
-        <v>0.277535450062252</v>
+        <v>0.179088516261758</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.134008407408617</v>
+        <v>0.166048222088383</v>
       </c>
       <c r="R14" t="n">
-        <v>0.423879739556481</v>
+        <v>-0.351081078146986</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.255726819423687</v>
+        <v>-0.343721783078336</v>
       </c>
       <c r="T14" t="n">
-        <v>0.248343068848541</v>
+        <v>0.284662343294648</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.177708831170551</v>
+        <v>-0.271403649121554</v>
       </c>
       <c r="V14" t="n">
-        <v>0.241414625038731</v>
+        <v>-0.147731673815484</v>
       </c>
       <c r="W14" t="n">
-        <v>0.231437325446221</v>
+        <v>-0.226633094022397</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0515563975486898</v>
+        <v>0.0464177725230712</v>
       </c>
     </row>
     <row r="15">
@@ -1522,73 +1522,73 @@
         <v>37</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.103601337656224</v>
+        <v>-0.107611287974307</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0638047643246787</v>
+        <v>0.0986035155659047</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0677208672898361</v>
+        <v>-0.111795509631347</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.167433010735661</v>
+        <v>0.244494692005924</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0761910246950262</v>
+        <v>-0.134827074816558</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0476845035217955</v>
+        <v>0.0692478754700038</v>
       </c>
       <c r="H15" t="n">
-        <v>0.303295483657674</v>
+        <v>0.327612536305896</v>
       </c>
       <c r="I15" t="n">
-        <v>0.17499189014498</v>
+        <v>0.140433783090419</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0244699696566971</v>
+        <v>-0.00558250547213327</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0501677367233686</v>
+        <v>0.0525672142943702</v>
       </c>
       <c r="L15" t="n">
-        <v>0.173087265689637</v>
+        <v>0.159446035215391</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0131922281130177</v>
+        <v>0.00334823984881238</v>
       </c>
       <c r="N15" t="n">
-        <v>0.231382753448115</v>
+        <v>0.248037061305785</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0987442924146908</v>
+        <v>0.184479106527165</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.446727791355299</v>
+        <v>-0.457478551456263</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.301688899220866</v>
+        <v>0.215904725630225</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.160919952653275</v>
+        <v>0.028899382983298</v>
       </c>
       <c r="S15" t="n">
-        <v>0.118354837290237</v>
+        <v>0.173459629315947</v>
       </c>
       <c r="T15" t="n">
-        <v>0.269553592420501</v>
+        <v>0.267555134673117</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.320297799573667</v>
+        <v>-0.282082048918823</v>
       </c>
       <c r="V15" t="n">
-        <v>0.139045388922185</v>
+        <v>0.0510016276686299</v>
       </c>
       <c r="W15" t="n">
-        <v>0.424227608181958</v>
+        <v>-0.427653168501074</v>
       </c>
       <c r="X15" t="n">
-        <v>0.142519629478749</v>
+        <v>0.0956193684440012</v>
       </c>
     </row>
     <row r="16">
@@ -1596,73 +1596,73 @@
         <v>38</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.181309185550671</v>
+        <v>-0.183768851075192</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0353891586512133</v>
+        <v>-0.0154751201334861</v>
       </c>
       <c r="D16" t="n">
-        <v>0.140222888304311</v>
+        <v>-0.168346711567778</v>
       </c>
       <c r="E16" t="n">
-        <v>0.303477244162211</v>
+        <v>-0.254486523080355</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0023162350976592</v>
+        <v>-0.034518650883656</v>
       </c>
       <c r="G16" t="n">
-        <v>0.11580627957118</v>
+        <v>0.140373001105467</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0744307743140565</v>
+        <v>0.140148822177593</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0288952807253238</v>
+        <v>-0.00658904687159977</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0812992885544168</v>
+        <v>0.0754676430247687</v>
       </c>
       <c r="K16" t="n">
-        <v>0.240557558687712</v>
+        <v>0.260408565304206</v>
       </c>
       <c r="L16" t="n">
-        <v>0.132418526296473</v>
+        <v>0.0846587009304054</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.00243839561240133</v>
+        <v>0.0352030754909959</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0136806804561966</v>
+        <v>0.026772970488309</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0637672454636528</v>
+        <v>0.0405148905740189</v>
       </c>
       <c r="P16" t="n">
-        <v>0.181473246375334</v>
+        <v>0.153098444208987</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.125049321636151</v>
+        <v>0.198440396173554</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.164915357055543</v>
+        <v>0.158325504130805</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.234809321170465</v>
+        <v>-0.1809676801117</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0866923886958279</v>
+        <v>0.0579009726338888</v>
       </c>
       <c r="U16" t="n">
-        <v>0.285173575525551</v>
+        <v>0.27034906814148</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0312239801016945</v>
+        <v>-0.103113827901236</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0721734982623346</v>
+        <v>0.0590057359235555</v>
       </c>
       <c r="X16" t="n">
-        <v>0.722582142350333</v>
+        <v>0.732695327268103</v>
       </c>
     </row>
     <row r="17">
@@ -1670,73 +1670,73 @@
         <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.248895033843691</v>
+        <v>-0.247656844314675</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0578426210641861</v>
+        <v>0.0508302193824383</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.299294162309583</v>
+        <v>0.296596503415452</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.300993639213559</v>
+        <v>0.308334783306601</v>
       </c>
       <c r="F17" t="n">
-        <v>0.185786406757894</v>
+        <v>-0.200957271075332</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0849555142187301</v>
+        <v>0.0665597968129061</v>
       </c>
       <c r="H17" t="n">
-        <v>0.100931704099867</v>
+        <v>0.0352735123717245</v>
       </c>
       <c r="I17" t="n">
-        <v>0.159664577047712</v>
+        <v>0.117253105675445</v>
       </c>
       <c r="J17" t="n">
-        <v>0.068741238420895</v>
+        <v>0.044672972115053</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.184987017587164</v>
+        <v>-0.230384117731121</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0843252229559966</v>
+        <v>-0.0648315727464218</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.11023367593024</v>
+        <v>-0.0976585741362284</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.00641525046331641</v>
+        <v>0.00847415865926792</v>
       </c>
       <c r="O17" t="n">
-        <v>0.14431368509241</v>
+        <v>0.0469260385588184</v>
       </c>
       <c r="P17" t="n">
-        <v>0.495016922087087</v>
+        <v>0.499996057271859</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.27111088474902</v>
+        <v>-0.058033521960417</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.491538141069911</v>
+        <v>0.567534305142302</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0877456703286724</v>
+        <v>0.129167291421509</v>
       </c>
       <c r="T17" t="n">
-        <v>0.124301312483987</v>
+        <v>0.125312729598635</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.00349513765881281</v>
+        <v>-0.0384955811874345</v>
       </c>
       <c r="V17" t="n">
-        <v>0.078698246957445</v>
+        <v>-0.0627822765516077</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0923517762031812</v>
+        <v>-0.0941606719348001</v>
       </c>
       <c r="X17" t="n">
-        <v>0.00217889634279637</v>
+        <v>-0.00359700991078932</v>
       </c>
     </row>
     <row r="18">
@@ -1744,73 +1744,73 @@
         <v>40</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.23878886613613</v>
+        <v>-0.23810600299078</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.146481917471697</v>
+        <v>0.139170869376085</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.065778037660729</v>
+        <v>0.0807333831124958</v>
       </c>
       <c r="E18" t="n">
-        <v>0.118050038447876</v>
+        <v>-0.129293895954429</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0913723428333373</v>
+        <v>-0.08513663640525</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.102155366868128</v>
+        <v>-0.0994228182305495</v>
       </c>
       <c r="H18" t="n">
-        <v>0.223424375648986</v>
+        <v>0.103335677755683</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.567060832347772</v>
+        <v>-0.609466345106651</v>
       </c>
       <c r="J18" t="n">
-        <v>0.222325486353393</v>
+        <v>0.253521150609449</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.222090197200111</v>
+        <v>-0.210280141047972</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0202266104324712</v>
+        <v>0.00528301670164063</v>
       </c>
       <c r="M18" t="n">
-        <v>0.461091157090445</v>
+        <v>0.409651880701502</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.217235283657475</v>
+        <v>-0.258521595881567</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0604810272679519</v>
+        <v>0.0230084626865254</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0926750236498217</v>
+        <v>-0.142642567077935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0471364681998285</v>
+        <v>-0.0169808688302059</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.127809570613964</v>
+        <v>0.124961805754697</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0850531315735177</v>
+        <v>0.0839757937825666</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.219076388843452</v>
+        <v>-0.212149761609823</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.117451730755863</v>
+        <v>-0.0457761682713852</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.169842269796492</v>
+        <v>0.199739860145802</v>
       </c>
       <c r="W18" t="n">
-        <v>0.151865203279609</v>
+        <v>-0.159180662068958</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0480071936490764</v>
+        <v>0.0458843703784155</v>
       </c>
     </row>
     <row r="19">
@@ -1818,73 +1818,73 @@
         <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.145432233054644</v>
+        <v>-0.148181151030258</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0571402393013674</v>
+        <v>0.0803668150932578</v>
       </c>
       <c r="D19" t="n">
-        <v>0.102488797086828</v>
+        <v>-0.130009093925658</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0345108950825035</v>
+        <v>0.0173923747449151</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0579193980929454</v>
+        <v>-0.0923163045585334</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0575132905996128</v>
+        <v>0.0701623627817081</v>
       </c>
       <c r="H19" t="n">
-        <v>0.125681902747453</v>
+        <v>0.158757317314163</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0542942763587411</v>
+        <v>0.0597285276792954</v>
       </c>
       <c r="J19" t="n">
-        <v>0.219698950314712</v>
+        <v>0.206125863404152</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0571606932324935</v>
+        <v>0.0748684115354725</v>
       </c>
       <c r="L19" t="n">
-        <v>0.202871018619666</v>
+        <v>0.172433183871127</v>
       </c>
       <c r="M19" t="n">
-        <v>0.00318910709021131</v>
+        <v>0.0492631710157477</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0457112825866588</v>
+        <v>0.0684435082600365</v>
       </c>
       <c r="O19" t="n">
-        <v>0.115112615328239</v>
+        <v>0.104287739136381</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.103146926057719</v>
+        <v>-0.0470750880664645</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.238582639439952</v>
+        <v>-0.231325230046162</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0177227835429325</v>
+        <v>0.0767364567372694</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.298113626586471</v>
+        <v>-0.303793859687672</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.366562515664084</v>
+        <v>-0.340166510852388</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.173324245092597</v>
+        <v>-0.473347846598878</v>
       </c>
       <c r="V19" t="n">
-        <v>0.657629673000867</v>
+        <v>-0.489267879126607</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.261842128332102</v>
+        <v>0.272945477872832</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0908117538518196</v>
+        <v>-0.0937454691945353</v>
       </c>
     </row>
     <row r="20">
@@ -1892,73 +1892,73 @@
         <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.256008695031139</v>
+        <v>-0.256224354175033</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.16552465983144</v>
+        <v>0.160867303645863</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.214925370594925</v>
+        <v>0.217822621428223</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.242538263248026</v>
+        <v>0.249736573867072</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0360075412834679</v>
+        <v>0.0259176489139452</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0692492617548668</v>
+        <v>-0.0623369765635707</v>
       </c>
       <c r="H20" t="n">
-        <v>0.181869276630177</v>
+        <v>0.130761392747769</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.206230697508415</v>
+        <v>-0.227654086101066</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0470270756864772</v>
+        <v>-0.0396315185490642</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0613688358107509</v>
+        <v>0.0912735029229901</v>
       </c>
       <c r="L20" t="n">
-        <v>0.162095665414856</v>
+        <v>0.144566927244199</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.10178794364729</v>
+        <v>-0.0499854365670072</v>
       </c>
       <c r="N20" t="n">
-        <v>0.306759351735006</v>
+        <v>0.335360323204925</v>
       </c>
       <c r="O20" t="n">
-        <v>0.479289967862648</v>
+        <v>0.395441287455113</v>
       </c>
       <c r="P20" t="n">
-        <v>0.173238429360857</v>
+        <v>0.311910489326422</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.178829277429208</v>
+        <v>0.0512244451330875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.462658706249105</v>
+        <v>-0.490733295146709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0852721109663596</v>
+        <v>-0.120598513272765</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0524126331928151</v>
+        <v>-0.0556810890800579</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0329026184707601</v>
+        <v>0.122588097455254</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.216610419437667</v>
+        <v>0.175190827999464</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.132542638175955</v>
+        <v>0.130317051665045</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.047718588331976</v>
+        <v>-0.0442191494190042</v>
       </c>
     </row>
     <row r="21">
@@ -1966,73 +1966,73 @@
         <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.18742678423151</v>
+        <v>-0.187313478913776</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0460172758052623</v>
+        <v>0.0439253863165473</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0821404202996738</v>
+        <v>0.0809232066835935</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0335249770910753</v>
+        <v>-0.0324383940988866</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0696942934671744</v>
+        <v>-0.0741607213068476</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0145654402861458</v>
+        <v>-0.0126120733035949</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0440057192713081</v>
+        <v>0.0390283596539758</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0657445273631938</v>
+        <v>-0.0691736801304388</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.298324818752623</v>
+        <v>-0.302406847950154</v>
       </c>
       <c r="K21" t="n">
-        <v>0.291908529933564</v>
+        <v>0.280916714413238</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0639889609438522</v>
+        <v>-0.0056077578826549</v>
       </c>
       <c r="M21" t="n">
-        <v>0.218670132798424</v>
+        <v>0.22963687565873</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0614158651671106</v>
+        <v>-0.0730716244005544</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.168860644318528</v>
+        <v>-0.115379647185672</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0921578002826463</v>
+        <v>-0.0468968569785541</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.415441328791946</v>
+        <v>0.474571464757491</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.258082929063227</v>
+        <v>0.136286473745503</v>
       </c>
       <c r="S21" t="n">
-        <v>0.207092713684824</v>
+        <v>0.261074442401981</v>
       </c>
       <c r="T21" t="n">
-        <v>0.16498311555556</v>
+        <v>0.1575889675394</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.137173293589869</v>
+        <v>-0.149339292452861</v>
       </c>
       <c r="V21" t="n">
-        <v>0.123739843237271</v>
+        <v>-0.0223684819385025</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.53892305225384</v>
+        <v>0.545341502555055</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.206844685970099</v>
+        <v>-0.206034660387658</v>
       </c>
     </row>
     <row r="22">
@@ -2040,73 +2040,73 @@
         <v>44</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.187084256946638</v>
+        <v>-0.189446700288231</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.194087008205834</v>
+        <v>0.213937356015497</v>
       </c>
       <c r="D22" t="n">
-        <v>0.11369181332563</v>
+        <v>-0.130868791280136</v>
       </c>
       <c r="E22" t="n">
-        <v>0.14618799254657</v>
+        <v>-0.101366373890936</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0831184993626858</v>
+        <v>0.0504950356492427</v>
       </c>
       <c r="G22" t="n">
-        <v>0.110738388448805</v>
+        <v>0.136811820984103</v>
       </c>
       <c r="H22" t="n">
-        <v>0.031436047131736</v>
+        <v>0.131770180975192</v>
       </c>
       <c r="I22" t="n">
-        <v>0.327574745069203</v>
+        <v>0.335284267573686</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.183922390791352</v>
+        <v>-0.205606079787022</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0536993296193252</v>
+        <v>-0.0102441128309258</v>
       </c>
       <c r="L22" t="n">
-        <v>0.354660708928357</v>
+        <v>0.412825476641843</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.246115680684044</v>
+        <v>-0.174225687812293</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.540155303333296</v>
+        <v>-0.493073224644134</v>
       </c>
       <c r="O22" t="n">
-        <v>0.184144500394814</v>
+        <v>0.0937100273194949</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.0392171073675384</v>
+        <v>0.0840214898755747</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.00914033750125626</v>
+        <v>-0.0862109048512826</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.00422308294999582</v>
+        <v>-0.0689524685928082</v>
       </c>
       <c r="S22" t="n">
-        <v>0.237947005568019</v>
+        <v>0.245612417013135</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.303301198078502</v>
+        <v>-0.309347375667246</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0929247406051975</v>
+        <v>0.0240153694685543</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.239809131857916</v>
+        <v>0.260897940465856</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0157882533909016</v>
+        <v>-0.0223350923419775</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0134250088368566</v>
+        <v>-0.0205140777097312</v>
       </c>
     </row>
     <row r="23">
@@ -2114,73 +2114,73 @@
         <v>45</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.241621179317565</v>
+        <v>-0.241415256942381</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.244583207475783</v>
+        <v>0.219281532200868</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.101643508905272</v>
+        <v>0.142561296941549</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0795696130588345</v>
+        <v>0.0220204341747857</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.363155003354561</v>
+        <v>0.440872270562636</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.386317823943472</v>
+        <v>-0.399652545509481</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.556973851213599</v>
+        <v>-0.390289535735358</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0736338808159416</v>
+        <v>0.211577110725943</v>
       </c>
       <c r="J23" t="n">
-        <v>0.345818319929863</v>
+        <v>0.381003430670656</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0245554255819592</v>
+        <v>0.0664167688052615</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0579463504380545</v>
+        <v>0.103627464236379</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.00655685905221991</v>
+        <v>-0.0665807144712877</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0514506209850569</v>
+        <v>0.0148588935406562</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0535984793035411</v>
+        <v>0.115690078957109</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.137867235453445</v>
+        <v>-0.181647227508357</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.187857051183686</v>
+        <v>0.185489956965107</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.179082089433481</v>
+        <v>0.101065331220424</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0976815003453718</v>
+        <v>0.138040191569168</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0178959287134294</v>
+        <v>-0.0339984439915725</v>
       </c>
       <c r="U23" t="n">
-        <v>0.176496414678426</v>
+        <v>0.114845882072371</v>
       </c>
       <c r="V23" t="n">
-        <v>0.107287633016884</v>
+        <v>-0.178632119873402</v>
       </c>
       <c r="W23" t="n">
-        <v>0.016152129338406</v>
+        <v>-0.0107673471213741</v>
       </c>
       <c r="X23" t="n">
-        <v>0.010207343916166</v>
+        <v>0.0158286968867172</v>
       </c>
     </row>
     <row r="24">
@@ -2188,73 +2188,73 @@
         <v>46</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.21955252118309</v>
+        <v>-0.220908743986202</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.243935892399632</v>
+        <v>0.253848199952494</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0108901103422771</v>
+        <v>-0.0137935230335826</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.204111295273104</v>
+        <v>0.233817734043727</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.104161215277008</v>
+        <v>0.0711992611614461</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0946231096027657</v>
+        <v>0.117278555047322</v>
       </c>
       <c r="H24" t="n">
-        <v>0.289024075154052</v>
+        <v>0.237087367369318</v>
       </c>
       <c r="I24" t="n">
-        <v>0.342528778163178</v>
+        <v>0.250759261216409</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0809117557462207</v>
+        <v>0.0286131134158853</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0518045027387456</v>
+        <v>-0.167850834777322</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.10139954921083</v>
+        <v>-0.190953971180439</v>
       </c>
       <c r="M24" t="n">
-        <v>0.131835400458193</v>
+        <v>0.185075699921896</v>
       </c>
       <c r="N24" t="n">
-        <v>0.155385593433521</v>
+        <v>0.175197194169469</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.345020262295825</v>
+        <v>-0.304606585614337</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.320914701148754</v>
+        <v>-0.322409742879558</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.223786894729763</v>
+        <v>-0.265510529452393</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.0183951883638042</v>
+        <v>0.056927042543203</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.149097518006653</v>
+        <v>-0.124943296751449</v>
       </c>
       <c r="T24" t="n">
-        <v>0.00139756170627253</v>
+        <v>-0.0304121279969711</v>
       </c>
       <c r="U24" t="n">
-        <v>0.256279782654608</v>
+        <v>0.390303178532407</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.339534740472796</v>
+        <v>0.183030963679486</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.304810187750654</v>
+        <v>0.301222909813862</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.0161807471234376</v>
+        <v>0.00211766863829425</v>
       </c>
     </row>
   </sheetData>

--- a/example1-metabolomics/results-A/pca/pca_norm_MaleMRD_MaleMHFD_FemMRD_FemMHFD.xlsx
+++ b/example1-metabolomics/results-A/pca/pca_norm_MaleMRD_MaleMHFD_FemMRD_FemMHFD.xlsx
@@ -560,73 +560,73 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.250133794220341</v>
+        <v>-0.251654854427229</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.261364355147002</v>
+        <v>0.252761786527895</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0739582217376572</v>
+        <v>-0.0784332793666552</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0166424772388387</v>
+        <v>0.00213513927764798</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.225026481698752</v>
+        <v>0.233791731995436</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0913074226421297</v>
+        <v>0.124643028715074</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.188778459554685</v>
+        <v>-0.195110669249412</v>
       </c>
       <c r="I2" t="n">
-        <v>0.319321045462256</v>
+        <v>0.305634319758928</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0570307224606482</v>
+        <v>-0.0233165565216358</v>
       </c>
       <c r="K2" t="n">
-        <v>0.173694237421022</v>
+        <v>0.286303766604613</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.540680406892767</v>
+        <v>-0.459759443336806</v>
       </c>
       <c r="M2" t="n">
-        <v>0.242758020391149</v>
+        <v>0.373850939907303</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0848485446206457</v>
+        <v>-0.0213479977326666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.369121327794835</v>
+        <v>0.29285761676048</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0917327039762728</v>
+        <v>-0.111757388656852</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0315997590160704</v>
+        <v>0.0793714688647742</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.102320215301899</v>
+        <v>0.067494592401229</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0204909722426489</v>
+        <v>0.0285065942537464</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.313650333661407</v>
+        <v>-0.314478041198057</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0175751433680067</v>
+        <v>0.0153569292642877</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0394883587067063</v>
+        <v>-0.0636614210817283</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.13452087394138</v>
+        <v>0.133149997204031</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00395403793952962</v>
+        <v>0.000493960811921814</v>
       </c>
     </row>
     <row r="3">
@@ -634,73 +634,73 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.201634110545817</v>
+        <v>-0.200905186844314</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0929748986985314</v>
+        <v>0.0984555496327298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.120448973663513</v>
+        <v>-0.141668937721742</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.186181815993656</v>
+        <v>0.214479509342595</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.225550200461541</v>
+        <v>0.202834603832974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0929428414542565</v>
+        <v>0.0963524899518486</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0372807205035996</v>
+        <v>0.0116192487521632</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0557090077175522</v>
+        <v>-0.0604915375843612</v>
       </c>
       <c r="J3" t="n">
-        <v>0.154736853891095</v>
+        <v>0.146900016083027</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.347565603591539</v>
+        <v>-0.373944850580485</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.127352909093815</v>
+        <v>-0.332062389054083</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.619024295903041</v>
+        <v>-0.509814869802926</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00399010220842863</v>
+        <v>-0.0031330790651203</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0934905864365593</v>
+        <v>-0.130682663756913</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.216623716232791</v>
+        <v>-0.130554432739444</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.397209040880249</v>
+        <v>0.418717771737041</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0579975499026318</v>
+        <v>-0.0456595183259408</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.17527396310163</v>
+        <v>-0.209815673629172</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.139608137951743</v>
+        <v>-0.11954912090984</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.019731917625688</v>
+        <v>-0.090281332589946</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0829985462412154</v>
+        <v>-0.0463902092091406</v>
       </c>
       <c r="W3" t="n">
-        <v>0.131536110938761</v>
+        <v>-0.127495877785474</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0419010884119626</v>
+        <v>-0.0405829513886226</v>
       </c>
     </row>
     <row r="4">
@@ -708,73 +708,73 @@
         <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.264373440842387</v>
+        <v>-0.265702291443741</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02739143892673</v>
+        <v>-0.049741415189584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.301746438062451</v>
+        <v>-0.28346720656957</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0156487602843564</v>
+        <v>-0.0242212674702412</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0562030268692791</v>
+        <v>0.0887740811210669</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.151661514846319</v>
+        <v>-0.128037363358409</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.208233104547813</v>
+        <v>-0.230040965887837</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.179492837559351</v>
+        <v>-0.240393860440976</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.433302208752979</v>
+        <v>-0.460241966308452</v>
       </c>
       <c r="K4" t="n">
-        <v>0.380158172086074</v>
+        <v>0.313951137253694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0837863519597499</v>
+        <v>0.0472570717536777</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.237613511051463</v>
+        <v>-0.252001113916649</v>
       </c>
       <c r="N4" t="n">
-        <v>0.016638807340357</v>
+        <v>-0.00110768383993813</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.198643644218377</v>
+        <v>-0.207089666449808</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232265956871486</v>
+        <v>-0.241056138141018</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.302850925589378</v>
+        <v>-0.324256237693994</v>
       </c>
       <c r="R4" t="n">
-        <v>0.170541349710642</v>
+        <v>-0.0707754266743559</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.273948294047583</v>
+        <v>-0.264656438150216</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.028684223137799</v>
+        <v>-0.030012955326541</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0728123976637045</v>
+        <v>-0.114708990930309</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0819118465875613</v>
+        <v>-0.0393081710513115</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.183995346787079</v>
+        <v>0.181511544770712</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0659388351629229</v>
+        <v>0.0716889227622797</v>
       </c>
     </row>
     <row r="5">
@@ -782,73 +782,73 @@
         <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.166865245070916</v>
+        <v>-0.16818961095858</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0932636591748192</v>
+        <v>0.0807332838793937</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0318387136520327</v>
+        <v>0.046526723943149</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.280592186505226</v>
+        <v>0.254212221428291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.208613881666319</v>
+        <v>-0.198399460713003</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.216525901998767</v>
+        <v>-0.265021658852903</v>
       </c>
       <c r="H5" t="n">
-        <v>0.248899466804898</v>
+        <v>0.253870761930093</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0310927183229831</v>
+        <v>0.067765635128304</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.47070914690647</v>
+        <v>-0.482578111245963</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.34174174161152</v>
+        <v>-0.298362565542742</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0549116720949142</v>
+        <v>-0.0900053200277276</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0368859179490425</v>
+        <v>0.0412321292399024</v>
       </c>
       <c r="N5" t="n">
-        <v>0.28848861024353</v>
+        <v>0.277234883639758</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.015437052522269</v>
+        <v>-0.024493590558733</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0322350061158124</v>
+        <v>0.0463900298188424</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0165193589961049</v>
+        <v>0.0201472345881147</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.000138999593875272</v>
+        <v>-0.0285484568453676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.218139273146386</v>
+        <v>0.190997319385123</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.219435235330028</v>
+        <v>-0.219158972923603</v>
       </c>
       <c r="U5" t="n">
-        <v>0.135824150554801</v>
+        <v>0.348598873366985</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.402407870708261</v>
+        <v>0.270660361139997</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.163015675082535</v>
+        <v>0.166074595082766</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01392642361097</v>
+        <v>-0.0189696095314694</v>
       </c>
     </row>
     <row r="6">
@@ -856,73 +856,73 @@
         <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0185392769547256</v>
+        <v>-0.0153867763159679</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0895006519252628</v>
+        <v>0.114203219179143</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.240984219084617</v>
+        <v>0.214443526599986</v>
       </c>
       <c r="E6" t="n">
-        <v>0.154169254975938</v>
+        <v>-0.135805628989074</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.352217413212905</v>
+        <v>0.382307357900888</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.781762561045048</v>
+        <v>-0.769330256237944</v>
       </c>
       <c r="H6" t="n">
-        <v>0.240369087856564</v>
+        <v>0.197404305951113</v>
       </c>
       <c r="I6" t="n">
-        <v>0.142006886304384</v>
+        <v>0.17675709129524</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0299402189607515</v>
+        <v>0.0825478234726865</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0351799490483556</v>
+        <v>0.0921968356173416</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.043770361804837</v>
+        <v>-0.0130379812709819</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0210364266328839</v>
+        <v>-0.0668851318978731</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.198150086130735</v>
+        <v>-0.227710385235498</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.109693010920016</v>
+        <v>-0.0596212970341578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.101479179412122</v>
+        <v>0.0873369008301957</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.026794729902107</v>
+        <v>0.0354946446296147</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0720937562975013</v>
+        <v>0.0790169328198981</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.134994326003901</v>
+        <v>-0.132627410900922</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0351079760329584</v>
+        <v>0.042753242893719</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0508078323143868</v>
+        <v>0.0118501970468329</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0426813630021442</v>
+        <v>-0.0564697124654559</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0190986470647924</v>
+        <v>-0.0183119087009403</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0206266007737464</v>
+        <v>0.0217653205595097</v>
       </c>
     </row>
     <row r="7">
@@ -930,73 +930,73 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.203075770252479</v>
+        <v>-0.203409317544776</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0710176698257305</v>
+        <v>0.0726552599524552</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0690250406820729</v>
+        <v>-0.0770521828767479</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0337341820640613</v>
+        <v>0.0400096072939198</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.270193597492195</v>
+        <v>0.264800256037705</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0699190852102786</v>
+        <v>0.0941824140427946</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0674379408902965</v>
+        <v>-0.0350049657976778</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.109002378848716</v>
+        <v>-0.120109009505307</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0413823437853988</v>
+        <v>0.0369305190294837</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0840947463521994</v>
+        <v>-0.112206685724416</v>
       </c>
       <c r="L7" t="n">
-        <v>0.059489956940421</v>
+        <v>-0.00714991667651356</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0967603135274559</v>
+        <v>-0.0577712715777229</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.273343625390155</v>
+        <v>-0.27544225441201</v>
       </c>
       <c r="O7" t="n">
-        <v>0.170164948997614</v>
+        <v>0.166697114003956</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.194261690819222</v>
+        <v>-0.318556854572434</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.34133173306815</v>
+        <v>-0.189716216948388</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.261087254432463</v>
+        <v>0.264625005036591</v>
       </c>
       <c r="S7" t="n">
-        <v>0.247918370535115</v>
+        <v>0.28617194367152</v>
       </c>
       <c r="T7" t="n">
-        <v>0.452075492731572</v>
+        <v>0.452107848777389</v>
       </c>
       <c r="U7" t="n">
-        <v>0.22999940444505</v>
+        <v>0.393131757444643</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.409270628716687</v>
+        <v>0.255896560091552</v>
       </c>
       <c r="W7" t="n">
-        <v>0.137692254959547</v>
+        <v>-0.127569597495265</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0228936931091011</v>
+        <v>0.00807453632106615</v>
       </c>
     </row>
     <row r="8">
@@ -1004,73 +1004,73 @@
         <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.265098543026144</v>
+        <v>-0.265472471778779</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.678087457078412</v>
+        <v>0.690185871274451</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.181697607495535</v>
+        <v>0.150819720129787</v>
       </c>
       <c r="E8" t="n">
-        <v>0.420388654823833</v>
+        <v>-0.39289037640264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.396277199211588</v>
+        <v>-0.420862795358006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0789391775574733</v>
+        <v>0.0497219151348885</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0984951883232223</v>
+        <v>0.0974074993051503</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.170680294143537</v>
+        <v>-0.166560817339454</v>
       </c>
       <c r="J8" t="n">
-        <v>0.058680453593818</v>
+        <v>0.0622706383885408</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0473723025203217</v>
+        <v>0.0284595415775917</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0755049967570031</v>
+        <v>0.0578278111499379</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0865358107230669</v>
+        <v>-0.106121167828043</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.136741886183853</v>
+        <v>-0.149568518804337</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.096050216222739</v>
+        <v>-0.0793791669111827</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0288590939327836</v>
+        <v>-0.0315024766132921</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0125567661576345</v>
+        <v>-0.00320269273662781</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0249979303314106</v>
+        <v>-0.0392632011485776</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0542969276438695</v>
+        <v>0.0477694710933052</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0534393375245903</v>
+        <v>-0.0515853400341372</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0089886149928597</v>
+        <v>-0.024768545060812</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0374494453149544</v>
+        <v>-0.0252681038832668</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0460322814719787</v>
+        <v>-0.0473323420227684</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0160284871321886</v>
+        <v>0.0168889173993757</v>
       </c>
     </row>
     <row r="9">
@@ -1078,73 +1078,73 @@
         <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.191922722423841</v>
+        <v>-0.192386917066347</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.158565689287214</v>
+        <v>0.151030640386282</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.162595221288392</v>
+        <v>0.173316620082533</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.394752699321388</v>
+        <v>0.368796051029586</v>
       </c>
       <c r="F9" t="n">
-        <v>0.191235389393066</v>
+        <v>-0.167610669454878</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.132782468244946</v>
+        <v>-0.155429259084432</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0291047469756026</v>
+        <v>-0.111621545467408</v>
       </c>
       <c r="I9" t="n">
-        <v>0.108951464260276</v>
+        <v>0.0987686796929875</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0459397899431504</v>
+        <v>-0.0751147184807562</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.218854971393032</v>
+        <v>-0.240375959814486</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0010026411818793</v>
+        <v>-0.0556930274780595</v>
       </c>
       <c r="M9" t="n">
-        <v>0.044956607773593</v>
+        <v>0.126090320020682</v>
       </c>
       <c r="N9" t="n">
-        <v>0.104385853443123</v>
+        <v>0.133644531256189</v>
       </c>
       <c r="O9" t="n">
-        <v>0.354121267978679</v>
+        <v>0.320564764356746</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00312735691248591</v>
+        <v>-0.0406555560455273</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.214110701512897</v>
+        <v>-0.272874821889306</v>
       </c>
       <c r="R9" t="n">
-        <v>0.174973885527279</v>
+        <v>-0.07074045452379</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.194520587417399</v>
+        <v>-0.161666318094315</v>
       </c>
       <c r="T9" t="n">
-        <v>0.390163146133502</v>
+        <v>0.373471125687912</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.23003512680189</v>
+        <v>-0.408429624718648</v>
       </c>
       <c r="V9" t="n">
-        <v>0.372815470289274</v>
+        <v>-0.200498463054481</v>
       </c>
       <c r="W9" t="n">
-        <v>0.194345597419185</v>
+        <v>-0.198332339663857</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0655390196381967</v>
+        <v>-0.0594234927472456</v>
       </c>
     </row>
     <row r="10">
@@ -1152,73 +1152,73 @@
         <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.15614484605849</v>
+        <v>-0.15392155779363</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0100157185957764</v>
+        <v>0.0299891947933991</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.191542080531799</v>
+        <v>0.16626139331242</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.180520643535108</v>
+        <v>0.225278620868889</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0257847409536108</v>
+        <v>-0.00856705201647836</v>
       </c>
       <c r="G10" t="n">
-        <v>0.13584815296402</v>
+        <v>0.114316359559874</v>
       </c>
       <c r="H10" t="n">
-        <v>0.136168115128639</v>
+        <v>0.0926528765952007</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0313401984679359</v>
+        <v>-0.0496455353661523</v>
       </c>
       <c r="J10" t="n">
-        <v>0.126351639924925</v>
+        <v>0.131862195494555</v>
       </c>
       <c r="K10" t="n">
-        <v>0.255525301110818</v>
+        <v>0.235474896252654</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0913582414164812</v>
+        <v>0.14403635485874</v>
       </c>
       <c r="M10" t="n">
-        <v>0.022094183142815</v>
+        <v>-0.0226042120546999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0223573795783332</v>
+        <v>-0.0322360386673475</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0312119148825671</v>
+        <v>0.0547154111098663</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0709218482945343</v>
+        <v>0.0723777577635026</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.127576213864041</v>
+        <v>0.0850402043014404</v>
       </c>
       <c r="R10" t="n">
-        <v>0.161882795595072</v>
+        <v>-0.169377126045608</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.27047555293419</v>
+        <v>-0.317585677415153</v>
       </c>
       <c r="T10" t="n">
-        <v>0.110063550437599</v>
+        <v>0.158307560404638</v>
       </c>
       <c r="U10" t="n">
-        <v>0.408768761404308</v>
+        <v>0.339367583719062</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.103521262624543</v>
+        <v>-0.0879176724486669</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.289026351629132</v>
+        <v>0.315236923121066</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.617984625949893</v>
+        <v>-0.620760086165387</v>
       </c>
     </row>
     <row r="11">
@@ -1226,73 +1226,73 @@
         <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.24241798566453</v>
+        <v>-0.243902432883797</v>
       </c>
       <c r="C11" t="n">
-        <v>0.250917274843247</v>
+        <v>-0.247346244335922</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.676279056301783</v>
+        <v>0.730184660417585</v>
       </c>
       <c r="E11" t="n">
-        <v>0.178896578897017</v>
+        <v>-0.261285144760354</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.136207219821008</v>
+        <v>0.210800201022996</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0694261152612344</v>
+        <v>0.153640803618397</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.488179788464065</v>
+        <v>-0.272951954348605</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.187102287512972</v>
+        <v>-0.189532838490495</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.144459649741986</v>
+        <v>-0.150082802175986</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.113640520759895</v>
+        <v>-0.101522791332117</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.099677294170525</v>
+        <v>-0.137900065290056</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0754629135626235</v>
+        <v>-0.0600469434985603</v>
       </c>
       <c r="N11" t="n">
-        <v>0.14191707907358</v>
+        <v>0.137168558401149</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0715700943354722</v>
+        <v>-0.0603040610284536</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0982088761475354</v>
+        <v>0.119393318666898</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0252115673278044</v>
+        <v>0.0013033911438044</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.01778605173951</v>
+        <v>0.0244579867006487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0654009183110075</v>
+        <v>0.0708004884945329</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0139703867091025</v>
+        <v>-0.0226698796980379</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0388450943247883</v>
+        <v>-0.0173919693949862</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00349467649757665</v>
+        <v>0.00808553437412882</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0306484227143215</v>
+        <v>0.0272744687704101</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00345530666228377</v>
+        <v>0.00505592969158372</v>
       </c>
     </row>
     <row r="12">
@@ -1300,73 +1300,73 @@
         <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.189283466830231</v>
+        <v>-0.192848383415186</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.30986318551486</v>
+        <v>0.288710775571476</v>
       </c>
       <c r="D12" t="n">
-        <v>0.124193992978512</v>
+        <v>-0.110857187325212</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.141239693924154</v>
+        <v>0.0886327193150183</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.298306189955992</v>
+        <v>0.329693230244734</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0280711811782259</v>
+        <v>0.0697851135192314</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.273028348140219</v>
+        <v>-0.266816906355881</v>
       </c>
       <c r="I12" t="n">
-        <v>0.225416883135404</v>
+        <v>0.182998864201492</v>
       </c>
       <c r="J12" t="n">
-        <v>0.131520328935247</v>
+        <v>0.0830832161375137</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.128973713186371</v>
+        <v>-0.206935619331104</v>
       </c>
       <c r="L12" t="n">
-        <v>0.476176338399296</v>
+        <v>0.541942143786804</v>
       </c>
       <c r="M12" t="n">
-        <v>0.30981042707976</v>
+        <v>0.167566735379014</v>
       </c>
       <c r="N12" t="n">
-        <v>0.284029216080931</v>
+        <v>0.271534640684776</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.355993946816962</v>
+        <v>-0.342919881127026</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0739332796298686</v>
+        <v>0.134832816442085</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.023034460697071</v>
+        <v>0.0195800512089147</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.179285689903236</v>
+        <v>0.196940687074534</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0412261190888507</v>
+        <v>0.0739764562883604</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0288109641333617</v>
+        <v>-0.0444285648036559</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.00951022511085771</v>
+        <v>-0.0227247248261178</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0891338742789128</v>
+        <v>-0.0927459762775305</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.0677891890065637</v>
+        <v>0.0628086460695196</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.0170011573577041</v>
+        <v>-0.0193503268488559</v>
       </c>
     </row>
     <row r="13">
@@ -1374,73 +1374,73 @@
         <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.200231012093647</v>
+        <v>-0.198761194829506</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0567170606518112</v>
+        <v>-0.0497864308091376</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0493950637217355</v>
+        <v>0.0378611849690282</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.279595633130325</v>
+        <v>0.309523983080153</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0539857722423381</v>
+        <v>-0.0783833589169155</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.00598676049864697</v>
+        <v>-0.0438808280706215</v>
       </c>
       <c r="H13" t="n">
-        <v>0.209759983707749</v>
+        <v>0.155361518634422</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.010378129644007</v>
+        <v>-0.0107932686932792</v>
       </c>
       <c r="J13" t="n">
-        <v>0.314708136246283</v>
+        <v>0.323917815104815</v>
       </c>
       <c r="K13" t="n">
-        <v>0.343055416867863</v>
+        <v>0.391455253084473</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.297606755005922</v>
+        <v>-0.190276548357471</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.207501427710237</v>
+        <v>-0.268339256224109</v>
       </c>
       <c r="N13" t="n">
-        <v>0.186156401800683</v>
+        <v>0.200352708002998</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.306296918938803</v>
+        <v>-0.216228120229928</v>
       </c>
       <c r="P13" t="n">
-        <v>0.199512187883631</v>
+        <v>0.157958701360958</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.240118360242394</v>
+        <v>-0.214954447848643</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.153134692531568</v>
+        <v>0.180375272159957</v>
       </c>
       <c r="S13" t="n">
-        <v>0.414626531007911</v>
+        <v>0.482182247605757</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0350014264890195</v>
+        <v>-0.004154733907567</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.202472648355445</v>
+        <v>-0.184704393864928</v>
       </c>
       <c r="V13" t="n">
-        <v>0.107563630607017</v>
+        <v>-0.0211096298800443</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0610296548924851</v>
+        <v>0.0540426643204823</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0430214204529474</v>
+        <v>-0.0386799497909055</v>
       </c>
     </row>
     <row r="14">
@@ -1448,73 +1448,73 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.249458403190426</v>
+        <v>-0.249929476535373</v>
       </c>
       <c r="C14" t="n">
-        <v>0.169797395698929</v>
+        <v>-0.179229571652267</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0994902829776912</v>
+        <v>-0.0839291261586621</v>
       </c>
       <c r="E14" t="n">
-        <v>0.020586506250491</v>
+        <v>-0.0227214579529996</v>
       </c>
       <c r="F14" t="n">
-        <v>0.257569105163938</v>
+        <v>-0.261311162765228</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0957122910937978</v>
+        <v>0.0748312593050564</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0276189258806833</v>
+        <v>0.0261683638570016</v>
       </c>
       <c r="I14" t="n">
-        <v>0.128780637088538</v>
+        <v>0.164393701729761</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0799461982513966</v>
+        <v>-0.054155616917148</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.152742133965749</v>
+        <v>-0.0822830205605321</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.177610909978849</v>
+        <v>-0.160379454372753</v>
       </c>
       <c r="M14" t="n">
-        <v>0.173834720745376</v>
+        <v>0.186618013832687</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.322597654323256</v>
+        <v>-0.318615039224661</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.281301680428051</v>
+        <v>-0.276911849544864</v>
       </c>
       <c r="P14" t="n">
-        <v>0.179088516261758</v>
+        <v>0.277535450062252</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.166048222088383</v>
+        <v>0.134008407408617</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.351081078146986</v>
+        <v>0.423879739556481</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.343721783078336</v>
+        <v>-0.255726819423687</v>
       </c>
       <c r="T14" t="n">
-        <v>0.284662343294648</v>
+        <v>0.248343068848541</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.271403649121554</v>
+        <v>-0.177708831170551</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.147731673815484</v>
+        <v>0.241414625038731</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.226633094022397</v>
+        <v>0.231437325446221</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0464177725230712</v>
+        <v>0.0515563975486898</v>
       </c>
     </row>
     <row r="15">
@@ -1522,73 +1522,73 @@
         <v>37</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.107611287974307</v>
+        <v>-0.103601337656224</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0986035155659047</v>
+        <v>-0.0638047643246787</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.111795509631347</v>
+        <v>0.0677208672898361</v>
       </c>
       <c r="E15" t="n">
-        <v>0.244494692005924</v>
+        <v>-0.167433010735661</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.134827074816558</v>
+        <v>0.0761910246950262</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0692478754700038</v>
+        <v>0.0476845035217955</v>
       </c>
       <c r="H15" t="n">
-        <v>0.327612536305896</v>
+        <v>0.303295483657674</v>
       </c>
       <c r="I15" t="n">
-        <v>0.140433783090419</v>
+        <v>0.17499189014498</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.00558250547213327</v>
+        <v>0.0244699696566971</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0525672142943702</v>
+        <v>0.0501677367233686</v>
       </c>
       <c r="L15" t="n">
-        <v>0.159446035215391</v>
+        <v>0.173087265689637</v>
       </c>
       <c r="M15" t="n">
-        <v>0.00334823984881238</v>
+        <v>-0.0131922281130177</v>
       </c>
       <c r="N15" t="n">
-        <v>0.248037061305785</v>
+        <v>0.231382753448115</v>
       </c>
       <c r="O15" t="n">
-        <v>0.184479106527165</v>
+        <v>0.0987442924146908</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.457478551456263</v>
+        <v>-0.446727791355299</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.215904725630225</v>
+        <v>0.301688899220866</v>
       </c>
       <c r="R15" t="n">
-        <v>0.028899382983298</v>
+        <v>-0.160919952653275</v>
       </c>
       <c r="S15" t="n">
-        <v>0.173459629315947</v>
+        <v>0.118354837290237</v>
       </c>
       <c r="T15" t="n">
-        <v>0.267555134673117</v>
+        <v>0.269553592420501</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.282082048918823</v>
+        <v>-0.320297799573667</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0510016276686299</v>
+        <v>0.139045388922185</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.427653168501074</v>
+        <v>0.424227608181958</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0956193684440012</v>
+        <v>0.142519629478749</v>
       </c>
     </row>
     <row r="16">
@@ -1596,73 +1596,73 @@
         <v>38</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.183768851075192</v>
+        <v>-0.181309185550671</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0154751201334861</v>
+        <v>0.0353891586512133</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.168346711567778</v>
+        <v>0.140222888304311</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.254486523080355</v>
+        <v>0.303477244162211</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.034518650883656</v>
+        <v>-0.0023162350976592</v>
       </c>
       <c r="G16" t="n">
-        <v>0.140373001105467</v>
+        <v>0.11580627957118</v>
       </c>
       <c r="H16" t="n">
-        <v>0.140148822177593</v>
+        <v>0.0744307743140565</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.00658904687159977</v>
+        <v>-0.0288952807253238</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0754676430247687</v>
+        <v>0.0812992885544168</v>
       </c>
       <c r="K16" t="n">
-        <v>0.260408565304206</v>
+        <v>0.240557558687712</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0846587009304054</v>
+        <v>0.132418526296473</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0352030754909959</v>
+        <v>-0.00243839561240133</v>
       </c>
       <c r="N16" t="n">
-        <v>0.026772970488309</v>
+        <v>0.0136806804561966</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0405148905740189</v>
+        <v>0.0637672454636528</v>
       </c>
       <c r="P16" t="n">
-        <v>0.153098444208987</v>
+        <v>0.181473246375334</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.198440396173554</v>
+        <v>0.125049321636151</v>
       </c>
       <c r="R16" t="n">
-        <v>0.158325504130805</v>
+        <v>-0.164915357055543</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1809676801117</v>
+        <v>-0.234809321170465</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0579009726338888</v>
+        <v>0.0866923886958279</v>
       </c>
       <c r="U16" t="n">
-        <v>0.27034906814148</v>
+        <v>0.285173575525551</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.103113827901236</v>
+        <v>-0.0312239801016945</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0590057359235555</v>
+        <v>-0.0721734982623346</v>
       </c>
       <c r="X16" t="n">
-        <v>0.732695327268103</v>
+        <v>0.722582142350333</v>
       </c>
     </row>
     <row r="17">
@@ -1670,73 +1670,73 @@
         <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.247656844314675</v>
+        <v>-0.248895033843691</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0508302193824383</v>
+        <v>-0.0578426210641861</v>
       </c>
       <c r="D17" t="n">
-        <v>0.296596503415452</v>
+        <v>-0.299294162309583</v>
       </c>
       <c r="E17" t="n">
-        <v>0.308334783306601</v>
+        <v>-0.300993639213559</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.200957271075332</v>
+        <v>0.185786406757894</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0665597968129061</v>
+        <v>0.0849555142187301</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0352735123717245</v>
+        <v>0.100931704099867</v>
       </c>
       <c r="I17" t="n">
-        <v>0.117253105675445</v>
+        <v>0.159664577047712</v>
       </c>
       <c r="J17" t="n">
-        <v>0.044672972115053</v>
+        <v>0.068741238420895</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.230384117731121</v>
+        <v>-0.184987017587164</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0648315727464218</v>
+        <v>-0.0843252229559966</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0976585741362284</v>
+        <v>-0.11023367593024</v>
       </c>
       <c r="N17" t="n">
-        <v>0.00847415865926792</v>
+        <v>-0.00641525046331641</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0469260385588184</v>
+        <v>0.14431368509241</v>
       </c>
       <c r="P17" t="n">
-        <v>0.499996057271859</v>
+        <v>0.495016922087087</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.058033521960417</v>
+        <v>-0.27111088474902</v>
       </c>
       <c r="R17" t="n">
-        <v>0.567534305142302</v>
+        <v>-0.491538141069911</v>
       </c>
       <c r="S17" t="n">
-        <v>0.129167291421509</v>
+        <v>0.0877456703286724</v>
       </c>
       <c r="T17" t="n">
-        <v>0.125312729598635</v>
+        <v>0.124301312483987</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0384955811874345</v>
+        <v>-0.00349513765881281</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0627822765516077</v>
+        <v>0.078698246957445</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0941606719348001</v>
+        <v>0.0923517762031812</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.00359700991078932</v>
+        <v>0.00217889634279637</v>
       </c>
     </row>
     <row r="18">
@@ -1744,73 +1744,73 @@
         <v>40</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.23810600299078</v>
+        <v>-0.23878886613613</v>
       </c>
       <c r="C18" t="n">
-        <v>0.139170869376085</v>
+        <v>-0.146481917471697</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0807333831124958</v>
+        <v>-0.065778037660729</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.129293895954429</v>
+        <v>0.118050038447876</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.08513663640525</v>
+        <v>0.0913723428333373</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0994228182305495</v>
+        <v>-0.102155366868128</v>
       </c>
       <c r="H18" t="n">
-        <v>0.103335677755683</v>
+        <v>0.223424375648986</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.609466345106651</v>
+        <v>-0.567060832347772</v>
       </c>
       <c r="J18" t="n">
-        <v>0.253521150609449</v>
+        <v>0.222325486353393</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.210280141047972</v>
+        <v>-0.222090197200111</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00528301670164063</v>
+        <v>0.0202266104324712</v>
       </c>
       <c r="M18" t="n">
-        <v>0.409651880701502</v>
+        <v>0.461091157090445</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.258521595881567</v>
+        <v>-0.217235283657475</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0230084626865254</v>
+        <v>-0.0604810272679519</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.142642567077935</v>
+        <v>-0.0926750236498217</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0169808688302059</v>
+        <v>-0.0471364681998285</v>
       </c>
       <c r="R18" t="n">
-        <v>0.124961805754697</v>
+        <v>-0.127809570613964</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0839757937825666</v>
+        <v>0.0850531315735177</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.212149761609823</v>
+        <v>-0.219076388843452</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0457761682713852</v>
+        <v>-0.117451730755863</v>
       </c>
       <c r="V18" t="n">
-        <v>0.199739860145802</v>
+        <v>-0.169842269796492</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.159180662068958</v>
+        <v>0.151865203279609</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0458843703784155</v>
+        <v>0.0480071936490764</v>
       </c>
     </row>
     <row r="19">
@@ -1818,73 +1818,73 @@
         <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.148181151030258</v>
+        <v>-0.145432233054644</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0803668150932578</v>
+        <v>-0.0571402393013674</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.130009093925658</v>
+        <v>0.102488797086828</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0173923747449151</v>
+        <v>0.0345108950825035</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0923163045585334</v>
+        <v>0.0579193980929454</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0701623627817081</v>
+        <v>0.0575132905996128</v>
       </c>
       <c r="H19" t="n">
-        <v>0.158757317314163</v>
+        <v>0.125681902747453</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0597285276792954</v>
+        <v>0.0542942763587411</v>
       </c>
       <c r="J19" t="n">
-        <v>0.206125863404152</v>
+        <v>0.219698950314712</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0748684115354725</v>
+        <v>0.0571606932324935</v>
       </c>
       <c r="L19" t="n">
-        <v>0.172433183871127</v>
+        <v>0.202871018619666</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0492631710157477</v>
+        <v>0.00318910709021131</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0684435082600365</v>
+        <v>0.0457112825866588</v>
       </c>
       <c r="O19" t="n">
-        <v>0.104287739136381</v>
+        <v>0.115112615328239</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0470750880664645</v>
+        <v>-0.103146926057719</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.231325230046162</v>
+        <v>-0.238582639439952</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0767364567372694</v>
+        <v>0.0177227835429325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.303793859687672</v>
+        <v>-0.298113626586471</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.340166510852388</v>
+        <v>-0.366562515664084</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.473347846598878</v>
+        <v>-0.173324245092597</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.489267879126607</v>
+        <v>0.657629673000867</v>
       </c>
       <c r="W19" t="n">
-        <v>0.272945477872832</v>
+        <v>-0.261842128332102</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0937454691945353</v>
+        <v>-0.0908117538518196</v>
       </c>
     </row>
     <row r="20">
@@ -1892,73 +1892,73 @@
         <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.256224354175033</v>
+        <v>-0.256008695031139</v>
       </c>
       <c r="C20" t="n">
-        <v>0.160867303645863</v>
+        <v>-0.16552465983144</v>
       </c>
       <c r="D20" t="n">
-        <v>0.217822621428223</v>
+        <v>-0.214925370594925</v>
       </c>
       <c r="E20" t="n">
-        <v>0.249736573867072</v>
+        <v>-0.242538263248026</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0259176489139452</v>
+        <v>-0.0360075412834679</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0623369765635707</v>
+        <v>-0.0692492617548668</v>
       </c>
       <c r="H20" t="n">
-        <v>0.130761392747769</v>
+        <v>0.181869276630177</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.227654086101066</v>
+        <v>-0.206230697508415</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0396315185490642</v>
+        <v>-0.0470270756864772</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0912735029229901</v>
+        <v>0.0613688358107509</v>
       </c>
       <c r="L20" t="n">
-        <v>0.144566927244199</v>
+        <v>0.162095665414856</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0499854365670072</v>
+        <v>-0.10178794364729</v>
       </c>
       <c r="N20" t="n">
-        <v>0.335360323204925</v>
+        <v>0.306759351735006</v>
       </c>
       <c r="O20" t="n">
-        <v>0.395441287455113</v>
+        <v>0.479289967862648</v>
       </c>
       <c r="P20" t="n">
-        <v>0.311910489326422</v>
+        <v>0.173238429360857</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0512244451330875</v>
+        <v>0.178829277429208</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.490733295146709</v>
+        <v>0.462658706249105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.120598513272765</v>
+        <v>-0.0852721109663596</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0556810890800579</v>
+        <v>-0.0524126331928151</v>
       </c>
       <c r="U20" t="n">
-        <v>0.122588097455254</v>
+        <v>0.0329026184707601</v>
       </c>
       <c r="V20" t="n">
-        <v>0.175190827999464</v>
+        <v>-0.216610419437667</v>
       </c>
       <c r="W20" t="n">
-        <v>0.130317051665045</v>
+        <v>-0.132542638175955</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0442191494190042</v>
+        <v>-0.047718588331976</v>
       </c>
     </row>
     <row r="21">
@@ -1966,73 +1966,73 @@
         <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.187313478913776</v>
+        <v>-0.18742678423151</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0439253863165473</v>
+        <v>-0.0460172758052623</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0809232066835935</v>
+        <v>-0.0821404202996738</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0324383940988866</v>
+        <v>0.0335249770910753</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0741607213068476</v>
+        <v>0.0696942934671744</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0126120733035949</v>
+        <v>-0.0145654402861458</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0390283596539758</v>
+        <v>0.0440057192713081</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0691736801304388</v>
+        <v>-0.0657445273631938</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.302406847950154</v>
+        <v>-0.298324818752623</v>
       </c>
       <c r="K21" t="n">
-        <v>0.280916714413238</v>
+        <v>0.291908529933564</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0056077578826549</v>
+        <v>0.0639889609438522</v>
       </c>
       <c r="M21" t="n">
-        <v>0.22963687565873</v>
+        <v>0.218670132798424</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0730716244005544</v>
+        <v>-0.0614158651671106</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.115379647185672</v>
+        <v>-0.168860644318528</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.0468968569785541</v>
+        <v>0.0921578002826463</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.474571464757491</v>
+        <v>0.415441328791946</v>
       </c>
       <c r="R21" t="n">
-        <v>0.136286473745503</v>
+        <v>-0.258082929063227</v>
       </c>
       <c r="S21" t="n">
-        <v>0.261074442401981</v>
+        <v>0.207092713684824</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1575889675394</v>
+        <v>0.16498311555556</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.149339292452861</v>
+        <v>-0.137173293589869</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0223684819385025</v>
+        <v>0.123739843237271</v>
       </c>
       <c r="W21" t="n">
-        <v>0.545341502555055</v>
+        <v>-0.53892305225384</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.206034660387658</v>
+        <v>-0.206844685970099</v>
       </c>
     </row>
     <row r="22">
@@ -2040,73 +2040,73 @@
         <v>44</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.189446700288231</v>
+        <v>-0.187084256946638</v>
       </c>
       <c r="C22" t="n">
-        <v>0.213937356015497</v>
+        <v>-0.194087008205834</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.130868791280136</v>
+        <v>0.11369181332563</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.101366373890936</v>
+        <v>0.14618799254657</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0504950356492427</v>
+        <v>-0.0831184993626858</v>
       </c>
       <c r="G22" t="n">
-        <v>0.136811820984103</v>
+        <v>0.110738388448805</v>
       </c>
       <c r="H22" t="n">
-        <v>0.131770180975192</v>
+        <v>0.031436047131736</v>
       </c>
       <c r="I22" t="n">
-        <v>0.335284267573686</v>
+        <v>0.327574745069203</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.205606079787022</v>
+        <v>-0.183922390791352</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0102441128309258</v>
+        <v>-0.0536993296193252</v>
       </c>
       <c r="L22" t="n">
-        <v>0.412825476641843</v>
+        <v>0.354660708928357</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.174225687812293</v>
+        <v>-0.246115680684044</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.493073224644134</v>
+        <v>-0.540155303333296</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0937100273194949</v>
+        <v>0.184144500394814</v>
       </c>
       <c r="P22" t="n">
-        <v>0.0840214898755747</v>
+        <v>-0.0392171073675384</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.0862109048512826</v>
+        <v>0.00914033750125626</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.0689524685928082</v>
+        <v>-0.00422308294999582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.245612417013135</v>
+        <v>0.237947005568019</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.309347375667246</v>
+        <v>-0.303301198078502</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0240153694685543</v>
+        <v>-0.0929247406051975</v>
       </c>
       <c r="V22" t="n">
-        <v>0.260897940465856</v>
+        <v>-0.239809131857916</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0223350923419775</v>
+        <v>0.0157882533909016</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0205140777097312</v>
+        <v>-0.0134250088368566</v>
       </c>
     </row>
     <row r="23">
@@ -2114,73 +2114,73 @@
         <v>45</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.241415256942381</v>
+        <v>-0.241621179317565</v>
       </c>
       <c r="C23" t="n">
-        <v>0.219281532200868</v>
+        <v>-0.244583207475783</v>
       </c>
       <c r="D23" t="n">
-        <v>0.142561296941549</v>
+        <v>-0.101643508905272</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0220204341747857</v>
+        <v>-0.0795696130588345</v>
       </c>
       <c r="F23" t="n">
-        <v>0.440872270562636</v>
+        <v>-0.363155003354561</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.399652545509481</v>
+        <v>-0.386317823943472</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.390289535735358</v>
+        <v>-0.556973851213599</v>
       </c>
       <c r="I23" t="n">
-        <v>0.211577110725943</v>
+        <v>0.0736338808159416</v>
       </c>
       <c r="J23" t="n">
-        <v>0.381003430670656</v>
+        <v>0.345818319929863</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0664167688052615</v>
+        <v>-0.0245554255819592</v>
       </c>
       <c r="L23" t="n">
-        <v>0.103627464236379</v>
+        <v>0.0579463504380545</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0665807144712877</v>
+        <v>-0.00655685905221991</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0148588935406562</v>
+        <v>0.0514506209850569</v>
       </c>
       <c r="O23" t="n">
-        <v>0.115690078957109</v>
+        <v>0.0535984793035411</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.181647227508357</v>
+        <v>-0.137867235453445</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.185489956965107</v>
+        <v>0.187857051183686</v>
       </c>
       <c r="R23" t="n">
-        <v>0.101065331220424</v>
+        <v>-0.179082089433481</v>
       </c>
       <c r="S23" t="n">
-        <v>0.138040191569168</v>
+        <v>0.0976815003453718</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0339984439915725</v>
+        <v>-0.0178959287134294</v>
       </c>
       <c r="U23" t="n">
-        <v>0.114845882072371</v>
+        <v>0.176496414678426</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.178632119873402</v>
+        <v>0.107287633016884</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0107673471213741</v>
+        <v>0.016152129338406</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0158286968867172</v>
+        <v>0.010207343916166</v>
       </c>
     </row>
     <row r="24">
@@ -2188,73 +2188,73 @@
         <v>46</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.220908743986202</v>
+        <v>-0.21955252118309</v>
       </c>
       <c r="C24" t="n">
-        <v>0.253848199952494</v>
+        <v>-0.243935892399632</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0137935230335826</v>
+        <v>0.0108901103422771</v>
       </c>
       <c r="E24" t="n">
-        <v>0.233817734043727</v>
+        <v>-0.204111295273104</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0711992611614461</v>
+        <v>-0.104161215277008</v>
       </c>
       <c r="G24" t="n">
-        <v>0.117278555047322</v>
+        <v>0.0946231096027657</v>
       </c>
       <c r="H24" t="n">
-        <v>0.237087367369318</v>
+        <v>0.289024075154052</v>
       </c>
       <c r="I24" t="n">
-        <v>0.250759261216409</v>
+        <v>0.342528778163178</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0286131134158853</v>
+        <v>0.0809117557462207</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.167850834777322</v>
+        <v>-0.0518045027387456</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.190953971180439</v>
+        <v>-0.10139954921083</v>
       </c>
       <c r="M24" t="n">
-        <v>0.185075699921896</v>
+        <v>0.131835400458193</v>
       </c>
       <c r="N24" t="n">
-        <v>0.175197194169469</v>
+        <v>0.155385593433521</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.304606585614337</v>
+        <v>-0.345020262295825</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.322409742879558</v>
+        <v>-0.320914701148754</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.265510529452393</v>
+        <v>-0.223786894729763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.056927042543203</v>
+        <v>-0.0183951883638042</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.124943296751449</v>
+        <v>-0.149097518006653</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0304121279969711</v>
+        <v>0.00139756170627253</v>
       </c>
       <c r="U24" t="n">
-        <v>0.390303178532407</v>
+        <v>0.256279782654608</v>
       </c>
       <c r="V24" t="n">
-        <v>0.183030963679486</v>
+        <v>-0.339534740472796</v>
       </c>
       <c r="W24" t="n">
-        <v>0.301222909813862</v>
+        <v>-0.304810187750654</v>
       </c>
       <c r="X24" t="n">
-        <v>0.00211766863829425</v>
+        <v>-0.0161807471234376</v>
       </c>
     </row>
   </sheetData>
